--- a/2026/PICHINCHA/Junio/PICHINCHA-Junio.xlsx
+++ b/2026/PICHINCHA/Junio/PICHINCHA-Junio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\PICHINCHA\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\PICHINCHA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5763F875-B88C-473E-B823-7656D3CE354D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10E2518-FC39-49E9-BD50-451B417F56CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,10 +18,15 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$46</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$10</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -238,9 +243,6 @@
     <t>SEGURO DE VIDA. SRA MONICA GOROSITO</t>
   </si>
   <si>
-    <t>SUBIDOS EN EN3R0</t>
-  </si>
-  <si>
     <t>PREVISION ORDINARIA</t>
   </si>
   <si>
@@ -265,13 +267,16 @@
     <t>JUNIO</t>
   </si>
   <si>
-    <t>Recuperacion de intereses por pago fuera de termino a administracion - Mes de MAYO - Debido a que la caja inicial pertenece a la administracion</t>
-  </si>
-  <si>
-    <t>ARBA</t>
-  </si>
-  <si>
     <t>ARTICULOS DE LIMPIEZA</t>
+  </si>
+  <si>
+    <t>SUBIDOS EN JUN10</t>
+  </si>
+  <si>
+    <t>ARBA CUOTA 1,2 Y 3</t>
+  </si>
+  <si>
+    <t>GASTOS BANCARIOS</t>
   </si>
 </sst>
 </file>
@@ -284,7 +289,7 @@
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,13 +398,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -457,7 +455,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="62">
     <border>
       <left/>
       <right/>
@@ -731,34 +729,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1111,6 +1083,145 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1119,7 +1230,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1132,17 +1243,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1161,18 +1261,13 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1185,15 +1280,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1222,23 +1313,18 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="6" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="10" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1247,66 +1333,62 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1318,30 +1400,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1351,61 +1421,121 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="52" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="54" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="60" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="51" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="51" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="61" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1484,9 +1614,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1524,9 +1654,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1559,9 +1689,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1594,9 +1741,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1773,65 +1937,65 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="108" t="s">
+      <c r="C2" s="88" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="23"/>
+      <c r="B5" s="18"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="109" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="19" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F7" s="89" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1839,412 +2003,420 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="28" t="s">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="120"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="97"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="129" t="s">
+      <c r="E11" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="129"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="51"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="128"/>
+      <c r="F11" s="99"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="123"/>
+      <c r="B12" s="123"/>
+      <c r="C12" s="95"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="55" t="s">
+      <c r="E12" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="56">
-        <v>-251627.60024926736</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="51" t="s">
+      <c r="F12" s="42">
+        <v>-353939.60624926729</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="154">
+      <c r="B13" s="123"/>
+      <c r="C13" s="95">
         <v>60602.69</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="57" t="s">
+      <c r="E13" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="127">
+      <c r="F13" s="98">
         <f>'prorrateo '!F10</f>
-        <v>417915.47400000005</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="121" t="s">
+        <v>702241.99200000009</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="124" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="123"/>
+      <c r="C14" s="95">
+        <v>22252</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="98">
+        <f>-(C39)</f>
+        <v>-718194.55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="124" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="124"/>
+      <c r="C15" s="95">
+        <v>119977</v>
+      </c>
+      <c r="D15" s="31"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="101"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="124" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="123" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="62">
+        <v>54000</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="101"/>
+      <c r="H16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="124" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="123"/>
+      <c r="C17" s="62">
+        <v>93972.61</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="101"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="124" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="124"/>
+      <c r="C18" s="95">
+        <v>57815.62</v>
+      </c>
+      <c r="E18" s="43"/>
+      <c r="F18" s="44"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="124" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="152">
-        <v>22252</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="127">
-        <f>-(C38)</f>
-        <v>-703945.02</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="121" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="122"/>
-      <c r="C15" s="154">
-        <v>119977</v>
-      </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="131" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="121" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="50" t="s">
+      <c r="B19" s="124"/>
+      <c r="C19" s="95">
+        <v>122100.6</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="44"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="124" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="124"/>
+      <c r="C20" s="95">
+        <v>37567.300000000003</v>
+      </c>
+      <c r="E20" s="43"/>
+      <c r="F20" s="44"/>
+      <c r="H20" s="87"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="125"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="69">
+        <f>SUM(C12:C20)</f>
+        <v>568287.82000000007</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="96">
+        <f>SUM(F12:F20)</f>
+        <v>-369892.16424926725</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="127" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="124"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="15"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="124" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="128"/>
+      <c r="C23" s="95">
+        <v>91370</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="15"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="124" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="128"/>
+      <c r="C24" s="95">
+        <v>5837.2</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="15"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="79">
-        <v>42700</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="131"/>
-      <c r="F16" s="132"/>
-      <c r="H16" t="s">
+      <c r="B25" s="128"/>
+      <c r="C25" s="95">
+        <v>49750</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="15"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="124" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="128"/>
+      <c r="C26" s="95">
+        <f>5899.06/2</f>
+        <v>2949.53</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="15"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="88" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="121" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="153">
-        <v>93972.61</v>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="132"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="121" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="122"/>
-      <c r="C18" s="152">
-        <v>57815.62</v>
-      </c>
-      <c r="E18" s="57"/>
-      <c r="F18" s="58"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="121" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="122"/>
-      <c r="C19" s="152">
-        <v>122100.6</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="58"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="121" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" s="122"/>
-      <c r="C20" s="152">
-        <v>37567.300000000003</v>
-      </c>
-      <c r="E20" s="57"/>
-      <c r="F20" s="58"/>
-      <c r="H20" s="106"/>
-    </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="123"/>
-      <c r="B21" s="124"/>
-      <c r="C21" s="86">
-        <f>SUM(C12:C20)</f>
-        <v>556987.82000000007</v>
-      </c>
-      <c r="E21" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="119">
-        <f>SUM(F12:F20)</f>
-        <v>-537657.14624926727</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="125" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="122"/>
-      <c r="C22" s="111"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="20"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="121" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="126"/>
-      <c r="C23" s="117">
-        <v>91370</v>
-      </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="121" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="126"/>
-      <c r="C24" s="152">
-        <v>5837.2</v>
-      </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="20"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="121" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="126"/>
-      <c r="C25" s="155">
-        <v>49750</v>
-      </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="20"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="110"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="32"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="107">
-        <f>SUM(C22:C26)</f>
-        <v>146957.20000000001</v>
-      </c>
+      <c r="B27" s="129"/>
+      <c r="C27" s="95"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="46" t="s">
+      <c r="E27" s="14"/>
+      <c r="F27" s="15"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="23"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="122">
+        <f>SUM(C22:C27)</f>
+        <v>149906.73000000001</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="48">
-        <f>+C27+C21</f>
-        <v>703945.02</v>
-      </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="20"/>
-    </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="68" t="s">
+      <c r="B29" s="34"/>
+      <c r="C29" s="35">
+        <f>+C28+C21</f>
+        <v>718194.55</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="15"/>
+    </row>
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="81"/>
-      <c r="C29" s="82"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="20"/>
-    </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="22" t="s">
+      <c r="B30" s="64"/>
+      <c r="C30" s="65"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="15"/>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="43"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="53"/>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="51"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="52">
-        <v>0</v>
-      </c>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="32"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="39"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="60"/>
-      <c r="B33" s="61"/>
-      <c r="C33" s="52">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="37"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="38">
         <v>0</v>
       </c>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="77"/>
-      <c r="B34" s="78"/>
-      <c r="C34" s="80"/>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="46"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="38">
+        <v>0</v>
+      </c>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="77"/>
-      <c r="B35" s="84"/>
-      <c r="C35" s="85"/>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="60"/>
+      <c r="B35" s="61"/>
+      <c r="C35" s="63"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="77"/>
-      <c r="B36" s="83"/>
-      <c r="C36" s="80">
-        <v>0</v>
-      </c>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="60"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="68"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="62" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="60"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="63">
+        <v>0</v>
+      </c>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="63"/>
-      <c r="C37" s="64">
-        <f>SUM(C32:C36)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="B38" s="49"/>
+      <c r="C38" s="50">
+        <f>SUM(C33:C37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="52">
-        <f>C28-C26</f>
-        <v>703945.02</v>
-      </c>
-      <c r="F38" s="6"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+      <c r="C39" s="38">
+        <f>C29-C27</f>
+        <v>718194.55</v>
+      </c>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="76">
-        <f>+C28</f>
-        <v>703945.02</v>
-      </c>
-      <c r="F39" s="6"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="62" t="s">
+      <c r="C40" s="59">
+        <f>+C29</f>
+        <v>718194.55</v>
+      </c>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="63"/>
-      <c r="C40" s="64">
-        <f>+C28+C37</f>
-        <v>703945.02</v>
-      </c>
-      <c r="E40" s="16"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D45" s="6"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="130"/>
-      <c r="C47" s="130"/>
-      <c r="D47" s="130"/>
-      <c r="E47" s="130"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="130"/>
-      <c r="C48" s="130"/>
-      <c r="D48" s="130"/>
-      <c r="E48" s="130"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B49" s="130"/>
-      <c r="C49" s="130"/>
-      <c r="D49" s="130"/>
-      <c r="E49" s="130"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="19"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="20"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="18"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="18"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="18"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="18"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="18"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="18"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="18"/>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="50">
+        <f>+C29+C38</f>
+        <v>718194.55</v>
+      </c>
+      <c r="E41" s="11"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="100"/>
+      <c r="C48" s="100"/>
+      <c r="D48" s="100"/>
+      <c r="E48" s="100"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="100"/>
+      <c r="C49" s="100"/>
+      <c r="D49" s="100"/>
+      <c r="E49" s="100"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="100"/>
+      <c r="C50" s="100"/>
+      <c r="D50" s="100"/>
+      <c r="E50" s="100"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="14"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="15"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="13"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="13"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="13"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="13"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="13"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="13"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B47:E49"/>
-    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="B48:E50"/>
     <mergeCell ref="F15:F17"/>
   </mergeCells>
   <hyperlinks>
@@ -2263,67 +2435,68 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="25" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="133" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="70">
-        <v>520227.48</v>
-      </c>
-      <c r="L1" s="70"/>
-      <c r="M1" s="27"/>
-    </row>
-    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="71" t="str">
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="135">
+        <f>'detalle y gastos'!C41</f>
+        <v>718194.55</v>
+      </c>
+      <c r="L1" s="135"/>
+      <c r="M1" s="136"/>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="137" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de JUNIO</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="74" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="75"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="138"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -2350,21 +2523,21 @@
       <c r="I3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="J3" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="113" t="s">
+      <c r="K3" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="30" t="s">
+      <c r="L3" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="139" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="2" t="s">
@@ -2377,366 +2550,366 @@
         <v>46</v>
       </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="35">
+      <c r="H4" s="25">
         <v>0.04</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="114" t="s">
+      <c r="K4" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="65" t="str">
+      <c r="L4" s="51" t="str">
         <f>'detalle y gastos'!F7</f>
         <v>Vto. 17/07</v>
       </c>
-      <c r="M4" s="65" t="s">
+      <c r="M4" s="140" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="141">
         <v>1</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="8">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="40">
-        <v>143100</v>
-      </c>
-      <c r="F5" s="79">
-        <f>E5</f>
-        <v>143100</v>
-      </c>
-      <c r="G5" s="66">
+      <c r="D5" s="12"/>
+      <c r="E5" s="30">
+        <v>108207</v>
+      </c>
+      <c r="F5" s="62">
+        <v>104050</v>
+      </c>
+      <c r="G5" s="52">
         <f>E5-F5</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="69">
+        <v>4157</v>
+      </c>
+      <c r="H5" s="55">
         <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="15">
-        <v>0</v>
-      </c>
-      <c r="J5" s="37">
+        <v>166.28</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0</v>
+      </c>
+      <c r="J5" s="27">
         <f>K$1/5</f>
+        <v>143638.91</v>
+      </c>
+      <c r="K5" s="94">
+        <f>K2*D5</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="10">
+        <f>J5+K5+H5+G5</f>
+        <v>147962.19</v>
+      </c>
+      <c r="M5" s="28">
+        <f>L5*4%+L5</f>
+        <v>153880.6776</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="141">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8">
+        <v>2</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="30">
         <v>104045.496</v>
       </c>
-      <c r="K5" s="115">
-        <f>K2*D5</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="15">
-        <f>J5+K5+H5+G5</f>
+      <c r="F6" s="62">
+        <f>E6</f>
         <v>104045.496</v>
       </c>
-      <c r="M5" s="38">
-        <f>L5*4%+L5</f>
-        <v>108207.31584</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13">
-        <v>2</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="40">
-        <v>137288.984</v>
-      </c>
-      <c r="F6" s="79">
-        <f>E6</f>
-        <v>137288.984</v>
-      </c>
-      <c r="G6" s="66">
+      <c r="G6" s="52">
         <f>E6-F6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="69">
+      <c r="H6" s="55">
         <f t="shared" ref="H6:H9" si="0">IF(G6&gt;0,G6*4%,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="15">
-        <v>0</v>
-      </c>
-      <c r="J6" s="37">
+      <c r="I6" s="10">
+        <v>0</v>
+      </c>
+      <c r="J6" s="27">
         <f t="shared" ref="J6:J9" si="1">K$1/5</f>
+        <v>143638.91</v>
+      </c>
+      <c r="K6" s="94">
+        <f>K2*D6</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="10">
+        <f>J6+K6+H6+G6</f>
+        <v>143638.91</v>
+      </c>
+      <c r="M6" s="28">
+        <f t="shared" ref="M6:M9" si="2">L6*4%+L6</f>
+        <v>149384.4664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="141">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8">
+        <v>3</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="30">
+        <v>247073.04560000001</v>
+      </c>
+      <c r="F7" s="62">
+        <v>143028</v>
+      </c>
+      <c r="G7" s="52">
+        <f t="shared" ref="G7:G8" si="3">E7-F7</f>
+        <v>104045.04560000001</v>
+      </c>
+      <c r="H7" s="55">
+        <f t="shared" si="0"/>
+        <v>4161.8018240000001</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
+      <c r="J7" s="27">
+        <f t="shared" si="1"/>
+        <v>143638.91</v>
+      </c>
+      <c r="K7" s="94">
+        <f>K2*D7</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <f>J7+K7+H7+G7</f>
+        <v>251845.75742400001</v>
+      </c>
+      <c r="M7" s="28">
+        <f t="shared" si="2"/>
+        <v>261919.58772096</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="141">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="30">
+        <v>247073.04560000001</v>
+      </c>
+      <c r="F8" s="62">
+        <f>104045+143028</f>
+        <v>247073</v>
+      </c>
+      <c r="G8" s="52">
+        <f t="shared" si="3"/>
+        <v>4.5600000012200326E-2</v>
+      </c>
+      <c r="H8" s="55">
+        <f t="shared" si="0"/>
+        <v>1.8240000004880132E-3</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0</v>
+      </c>
+      <c r="J8" s="27">
+        <f t="shared" si="1"/>
+        <v>143638.91</v>
+      </c>
+      <c r="K8" s="94">
+        <f>K2*D8</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="10">
+        <f>J8+K8+H8+G8</f>
+        <v>143638.95742400002</v>
+      </c>
+      <c r="M8" s="28">
+        <f t="shared" si="2"/>
+        <v>149384.51572096001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="142">
+        <v>5</v>
+      </c>
+      <c r="B9" s="143">
+        <v>5</v>
+      </c>
+      <c r="C9" s="144" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="145"/>
+      <c r="E9" s="146">
         <v>104045.496</v>
       </c>
-      <c r="K6" s="115">
-        <f>K2*D6</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="15">
-        <f>J6+K6+H6+G6</f>
+      <c r="F9" s="147">
+        <f>E9</f>
         <v>104045.496</v>
       </c>
-      <c r="M6" s="38">
-        <f t="shared" ref="M6:M9" si="2">L6*4%+L6</f>
-        <v>108207.31584</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
-        <v>3</v>
-      </c>
-      <c r="B7" s="13">
-        <v>3</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="40">
-        <v>137526.49000000002</v>
-      </c>
-      <c r="F7" s="79">
-        <v>0</v>
-      </c>
-      <c r="G7" s="66">
-        <f t="shared" ref="G7:G8" si="3">E7-F7</f>
-        <v>137526.49000000002</v>
-      </c>
-      <c r="H7" s="69">
+      <c r="G9" s="148">
+        <f>E9-F9</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="149">
         <f t="shared" si="0"/>
-        <v>5501.0596000000005</v>
-      </c>
-      <c r="I7" s="15">
-        <v>0</v>
-      </c>
-      <c r="J7" s="37">
+        <v>0</v>
+      </c>
+      <c r="I9" s="150">
+        <v>0</v>
+      </c>
+      <c r="J9" s="151">
         <f t="shared" si="1"/>
-        <v>104045.496</v>
-      </c>
-      <c r="K7" s="115">
-        <f>K2*D7</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="15">
-        <f>J7+K7+H7+G7</f>
-        <v>247073.04560000001</v>
-      </c>
-      <c r="M7" s="38">
+        <v>143638.91</v>
+      </c>
+      <c r="K9" s="152">
+        <f>K2*D9</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="150">
+        <f>J9+K9+H9+G9</f>
+        <v>143638.91</v>
+      </c>
+      <c r="M9" s="153">
         <f t="shared" si="2"/>
-        <v>256955.967424</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13">
-        <v>4</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="40">
-        <v>137526.49000000002</v>
-      </c>
-      <c r="F8" s="79">
-        <v>0</v>
-      </c>
-      <c r="G8" s="66">
-        <f t="shared" si="3"/>
-        <v>137526.49000000002</v>
-      </c>
-      <c r="H8" s="69">
-        <f t="shared" si="0"/>
-        <v>5501.0596000000005</v>
-      </c>
-      <c r="I8" s="15">
-        <v>0</v>
-      </c>
-      <c r="J8" s="37">
-        <f t="shared" si="1"/>
-        <v>104045.496</v>
-      </c>
-      <c r="K8" s="115">
-        <f>K2*D8</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="15">
-        <f>J8+K8+H8+G8</f>
-        <v>247073.04560000001</v>
-      </c>
-      <c r="M8" s="38">
-        <f t="shared" si="2"/>
-        <v>256955.967424</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
-        <v>5</v>
-      </c>
-      <c r="B9" s="13">
-        <v>5</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="40">
-        <v>137526.49000000002</v>
-      </c>
-      <c r="F9" s="79">
-        <f>E9</f>
-        <v>137526.49000000002</v>
-      </c>
-      <c r="G9" s="66">
-        <f>E9-F9</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="69">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="15">
-        <v>0</v>
-      </c>
-      <c r="J9" s="37">
-        <f t="shared" si="1"/>
-        <v>104045.496</v>
-      </c>
-      <c r="K9" s="115">
-        <f>K2*D9</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="15">
-        <f>J9+K9+H9+G9</f>
-        <v>104045.496</v>
-      </c>
-      <c r="M9" s="38">
-        <f t="shared" si="2"/>
-        <v>108207.31584</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+        <v>149384.4664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="44">
+      <c r="B10" s="155"/>
+      <c r="C10" s="156"/>
+      <c r="D10" s="157">
         <f t="shared" ref="D10:M10" si="4">SUM(D5:D9)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="159">
         <f t="shared" si="4"/>
-        <v>692968.45400000003</v>
-      </c>
-      <c r="F10" s="41">
+        <v>810444.08319999999</v>
+      </c>
+      <c r="F10" s="159">
         <f>SUM(F5:F9)</f>
-        <v>417915.47400000005</v>
-      </c>
-      <c r="G10" s="49">
+        <v>702241.99200000009</v>
+      </c>
+      <c r="G10" s="158">
         <f t="shared" si="4"/>
-        <v>275052.98000000004</v>
-      </c>
-      <c r="H10" s="49">
+        <v>108202.09120000002</v>
+      </c>
+      <c r="H10" s="159">
         <f t="shared" si="4"/>
-        <v>11002.119200000001</v>
-      </c>
-      <c r="I10" s="11">
+        <v>4328.0836480000007</v>
+      </c>
+      <c r="I10" s="162">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J10" s="45">
+      <c r="J10" s="161">
         <f t="shared" si="4"/>
-        <v>520227.48</v>
-      </c>
-      <c r="K10" s="45">
+        <v>718194.55</v>
+      </c>
+      <c r="K10" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L10" s="116">
+      <c r="L10" s="159">
         <f t="shared" si="4"/>
-        <v>806282.57920000004</v>
-      </c>
-      <c r="M10" s="116">
+        <v>830724.7248480001</v>
+      </c>
+      <c r="M10" s="159">
         <f t="shared" si="4"/>
-        <v>838533.88236799999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="133"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="133"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="133"/>
-      <c r="K11" s="133"/>
-      <c r="L11" s="133"/>
-      <c r="M11" s="133"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>863953.71384192002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="102"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="102"/>
+      <c r="K11" s="102"/>
+      <c r="L11" s="102"/>
+      <c r="M11" s="102"/>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="134"/>
-      <c r="D13" s="134"/>
-      <c r="E13" s="134"/>
-      <c r="F13" s="134"/>
-      <c r="G13" s="134"/>
-      <c r="H13" s="134"/>
-      <c r="I13" s="134"/>
-      <c r="J13" s="134"/>
-      <c r="K13" s="134"/>
-      <c r="L13" s="134"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="134"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="134"/>
-      <c r="F14" s="134"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="134"/>
-      <c r="I14" s="134"/>
-      <c r="J14" s="134"/>
-      <c r="K14" s="134"/>
-      <c r="L14" s="134"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="134"/>
-      <c r="D15" s="134"/>
-      <c r="E15" s="134"/>
-      <c r="F15" s="134"/>
-      <c r="G15" s="134"/>
-      <c r="H15" s="134"/>
-      <c r="I15" s="134"/>
-      <c r="J15" s="134"/>
-      <c r="K15" s="134"/>
-      <c r="L15" s="134"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="134"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="134"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="134"/>
-      <c r="H16" s="134"/>
-      <c r="I16" s="134"/>
-      <c r="J16" s="134"/>
-      <c r="K16" s="134"/>
-      <c r="L16" s="134"/>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="103"/>
+      <c r="K13" s="103"/>
+      <c r="L13" s="103"/>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="103"/>
+      <c r="K14" s="103"/>
+      <c r="L14" s="103"/>
+    </row>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="103"/>
+      <c r="K15" s="103"/>
+      <c r="L15" s="103"/>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="103"/>
+      <c r="H16" s="103"/>
+      <c r="I16" s="103"/>
+      <c r="J16" s="103"/>
+      <c r="K16" s="103"/>
+      <c r="L16" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2752,232 +2925,232 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="140" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-    </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="143" t="s">
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="146">
+      <c r="B2" s="113"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="115">
         <v>565</v>
       </c>
-      <c r="E2" s="147"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-    </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="148" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="148" t="s">
+      <c r="E2" s="116"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="117" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="148" t="s">
+      <c r="C3" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="150" t="s">
+      <c r="D3" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="135" t="s">
+      <c r="E3" s="104" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="135" t="s">
+      <c r="F3" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="135" t="s">
+      <c r="G3" s="104" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="149"/>
-      <c r="B4" s="149"/>
-      <c r="C4" s="149"/>
-      <c r="D4" s="151"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="89">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="118"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="72">
         <v>1</v>
       </c>
-      <c r="B5" s="91" t="s">
+      <c r="B5" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="90">
+      <c r="D5" s="73">
         <v>0.1512</v>
       </c>
-      <c r="E5" s="93">
+      <c r="E5" s="76">
         <v>85</v>
       </c>
-      <c r="F5" s="93">
-        <v>0</v>
-      </c>
-      <c r="G5" s="93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="89">
+      <c r="F5" s="76">
+        <v>0</v>
+      </c>
+      <c r="G5" s="76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="72">
         <v>2</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="90">
+      <c r="D6" s="73">
         <v>0.15690000000000001</v>
       </c>
-      <c r="E6" s="93">
+      <c r="E6" s="76">
         <v>89</v>
       </c>
-      <c r="F6" s="93">
-        <v>0</v>
-      </c>
-      <c r="G6" s="93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="89">
+      <c r="F6" s="76">
+        <v>0</v>
+      </c>
+      <c r="G6" s="76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="72">
         <v>3</v>
       </c>
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="92" t="s">
+      <c r="C7" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="90">
+      <c r="D7" s="73">
         <v>0.15820000000000001</v>
       </c>
-      <c r="E7" s="93">
+      <c r="E7" s="76">
         <v>89</v>
       </c>
-      <c r="F7" s="93">
-        <v>0</v>
-      </c>
-      <c r="G7" s="93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="89">
+      <c r="F7" s="76">
+        <v>0</v>
+      </c>
+      <c r="G7" s="76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="72">
         <v>4</v>
       </c>
-      <c r="B8" s="91" t="s">
+      <c r="B8" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="C8" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="90">
+      <c r="D8" s="73">
         <v>0.19800000000000001</v>
       </c>
-      <c r="E8" s="93">
+      <c r="E8" s="76">
         <v>112</v>
       </c>
-      <c r="F8" s="93">
-        <v>0</v>
-      </c>
-      <c r="G8" s="93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="89">
+      <c r="F8" s="76">
+        <v>0</v>
+      </c>
+      <c r="G8" s="76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="72">
         <v>5</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="92" t="s">
+      <c r="C9" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="90">
+      <c r="D9" s="73">
         <v>0.15920000000000001</v>
       </c>
-      <c r="E9" s="93">
+      <c r="E9" s="76">
         <v>90</v>
       </c>
-      <c r="F9" s="93">
-        <v>0</v>
-      </c>
-      <c r="G9" s="93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="94">
+      <c r="F9" s="76">
+        <v>0</v>
+      </c>
+      <c r="G9" s="76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="77">
         <v>6</v>
       </c>
-      <c r="B10" s="96" t="s">
+      <c r="B10" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="97" t="s">
+      <c r="C10" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="95">
+      <c r="D10" s="78">
         <v>0.17649999999999999</v>
       </c>
-      <c r="E10" s="98">
+      <c r="E10" s="81">
         <v>100</v>
       </c>
-      <c r="F10" s="98">
-        <v>0</v>
-      </c>
-      <c r="G10" s="98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="99" t="s">
+      <c r="F10" s="81">
+        <v>0</v>
+      </c>
+      <c r="G10" s="81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="100"/>
-      <c r="C11" s="100"/>
-      <c r="D11" s="101">
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="84">
         <v>1</v>
       </c>
-      <c r="E11" s="101">
+      <c r="E11" s="84">
         <v>565</v>
       </c>
-      <c r="F11" s="101" t="s">
+      <c r="F11" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="102" t="s">
+      <c r="G11" s="85" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="137"/>
-      <c r="B12" s="138"/>
-      <c r="C12" s="138"/>
-      <c r="D12" s="138"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="87"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="106"/>
+      <c r="B12" s="107"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/2026/PICHINCHA/Junio/PICHINCHA-Junio.xlsx
+++ b/2026/PICHINCHA/Junio/PICHINCHA-Junio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\PICHINCHA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10E2518-FC39-49E9-BD50-451B417F56CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E8EBEC-2FFE-4862-A332-3F53576C010F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -228,9 +228,6 @@
     <t>AYSA</t>
   </si>
   <si>
-    <t>VTO</t>
-  </si>
-  <si>
     <t>SEGUNDO</t>
   </si>
   <si>
@@ -258,9 +255,6 @@
     <t>METROGAS</t>
   </si>
   <si>
-    <t>Vto. 17/07</t>
-  </si>
-  <si>
     <t>Liquidacion mes de JUNIO</t>
   </si>
   <si>
@@ -277,6 +271,12 @@
   </si>
   <si>
     <t>GASTOS BANCARIOS</t>
+  </si>
+  <si>
+    <t>Vto. 15/07</t>
+  </si>
+  <si>
+    <t>VTO 19/07</t>
   </si>
 </sst>
 </file>
@@ -1406,72 +1406,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1497,9 +1431,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1536,6 +1467,75 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="51" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="61" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1989,10 +1989,10 @@
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
       <c r="E7" s="19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F7" s="89" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2015,14 +2015,14 @@
       <c r="B11" s="21"/>
       <c r="C11" s="97"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="99" t="s">
+      <c r="E11" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="99"/>
+      <c r="F11" s="141"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="123"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="101"/>
       <c r="C12" s="95"/>
       <c r="D12" s="5"/>
       <c r="E12" s="41" t="s">
@@ -2033,10 +2033,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="123" t="s">
+      <c r="A13" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="123"/>
+      <c r="B13" s="101"/>
       <c r="C13" s="95">
         <v>60602.69</v>
       </c>
@@ -2050,10 +2050,10 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="124" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="123"/>
+      <c r="A14" s="102" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="101"/>
       <c r="C14" s="95">
         <v>22252</v>
       </c>
@@ -2067,51 +2067,51 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="124"/>
+      <c r="B15" s="102"/>
       <c r="C15" s="95">
         <v>119977</v>
       </c>
       <c r="D15" s="31"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="101"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="143"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="123" t="s">
-        <v>77</v>
+      <c r="B16" s="101" t="s">
+        <v>75</v>
       </c>
       <c r="C16" s="62">
         <v>54000</v>
       </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="121"/>
-      <c r="F16" s="101"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="143"/>
       <c r="H16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="123"/>
+      <c r="A17" s="102" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="101"/>
       <c r="C17" s="62">
         <v>93972.61</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="101"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="143"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="124" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="124"/>
+      <c r="A18" s="102" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="102"/>
       <c r="C18" s="95">
         <v>57815.62</v>
       </c>
@@ -2119,10 +2119,10 @@
       <c r="F18" s="44"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="124" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" s="124"/>
+      <c r="A19" s="102" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="102"/>
       <c r="C19" s="95">
         <v>122100.6</v>
       </c>
@@ -2131,10 +2131,10 @@
       <c r="F19" s="44"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="124" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" s="124"/>
+      <c r="A20" s="102" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="102"/>
       <c r="C20" s="95">
         <v>37567.300000000003</v>
       </c>
@@ -2143,8 +2143,8 @@
       <c r="H20" s="87"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="125"/>
-      <c r="B21" s="126"/>
+      <c r="A21" s="103"/>
+      <c r="B21" s="104"/>
       <c r="C21" s="69">
         <f>SUM(C12:C20)</f>
         <v>568287.82000000007</v>
@@ -2158,20 +2158,20 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="127" t="s">
+      <c r="A22" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="124"/>
+      <c r="B22" s="102"/>
       <c r="C22" s="90"/>
       <c r="D22" s="5"/>
       <c r="E22" s="14"/>
       <c r="F22" s="15"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="124" t="s">
+      <c r="A23" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="128"/>
+      <c r="B23" s="106"/>
       <c r="C23" s="95">
         <v>91370</v>
       </c>
@@ -2180,10 +2180,10 @@
       <c r="F23" s="15"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="124" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="128"/>
+      <c r="A24" s="102" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="106"/>
       <c r="C24" s="95">
         <v>5837.2</v>
       </c>
@@ -2192,10 +2192,10 @@
       <c r="F24" s="15"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="124" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="128"/>
+      <c r="A25" s="102" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="106"/>
       <c r="C25" s="95">
         <v>49750</v>
       </c>
@@ -2204,10 +2204,10 @@
       <c r="F25" s="15"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="124" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" s="128"/>
+      <c r="A26" s="102" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="106"/>
       <c r="C26" s="95">
         <f>5899.06/2</f>
         <v>2949.53</v>
@@ -2218,9 +2218,9 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="88" t="s">
-        <v>70</v>
-      </c>
-      <c r="B27" s="129"/>
+        <v>69</v>
+      </c>
+      <c r="B27" s="107"/>
       <c r="C27" s="95"/>
       <c r="D27" s="5"/>
       <c r="E27" s="14"/>
@@ -2229,7 +2229,7 @@
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="23"/>
       <c r="B28" s="24"/>
-      <c r="C28" s="122">
+      <c r="C28" s="100">
         <f>SUM(C22:C27)</f>
         <v>149906.73000000001</v>
       </c>
@@ -2356,22 +2356,22 @@
       <c r="E47" s="11"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="100"/>
-      <c r="C48" s="100"/>
-      <c r="D48" s="100"/>
-      <c r="E48" s="100"/>
+      <c r="B48" s="142"/>
+      <c r="C48" s="142"/>
+      <c r="D48" s="142"/>
+      <c r="E48" s="142"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="100"/>
-      <c r="C49" s="100"/>
-      <c r="D49" s="100"/>
-      <c r="E49" s="100"/>
+      <c r="B49" s="142"/>
+      <c r="C49" s="142"/>
+      <c r="D49" s="142"/>
+      <c r="E49" s="142"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="100"/>
-      <c r="C50" s="100"/>
-      <c r="D50" s="100"/>
-      <c r="E50" s="100"/>
+      <c r="B50" s="142"/>
+      <c r="C50" s="142"/>
+      <c r="D50" s="142"/>
+      <c r="E50" s="142"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="14"/>
@@ -2449,34 +2449,34 @@
     <col min="10" max="10" width="17.85546875" customWidth="1"/>
     <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
     <col min="15" max="15" width="11.42578125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="130" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="133" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="111" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="135">
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="113">
         <f>'detalle y gastos'!C41</f>
         <v>718194.55</v>
       </c>
-      <c r="L1" s="135"/>
-      <c r="M1" s="136"/>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="str">
+      <c r="L1" s="113"/>
+      <c r="M1" s="114"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="115" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de JUNIO</v>
       </c>
@@ -2493,9 +2493,9 @@
       <c r="J2" s="57"/>
       <c r="K2" s="91"/>
       <c r="L2" s="91"/>
-      <c r="M2" s="138"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M2" s="116"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
         <v>0</v>
       </c>
@@ -2530,13 +2530,13 @@
         <v>38</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="M3" s="139" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M3" s="117" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2564,14 +2564,18 @@
       </c>
       <c r="L4" s="51" t="str">
         <f>'detalle y gastos'!F7</f>
-        <v>Vto. 17/07</v>
-      </c>
-      <c r="M4" s="140" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="141">
+        <v>Vto. 15/07</v>
+      </c>
+      <c r="M4" s="140" t="str">
+        <f>O4</f>
+        <v>VTO 19/07</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="118">
         <v>1</v>
       </c>
       <c r="B5" s="8">
@@ -2615,8 +2619,8 @@
         <v>153880.6776</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="141">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="118">
         <v>2</v>
       </c>
       <c r="B6" s="8">
@@ -2661,8 +2665,8 @@
         <v>149384.4664</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="141">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="118">
         <v>3</v>
       </c>
       <c r="B7" s="8">
@@ -2706,15 +2710,15 @@
         <v>261919.58772096</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="141">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="118">
         <v>4</v>
       </c>
       <c r="B8" s="8">
         <v>4</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="30">
@@ -2752,164 +2756,164 @@
         <v>149384.51572096001</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="142">
+    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="119">
         <v>5</v>
       </c>
-      <c r="B9" s="143">
+      <c r="B9" s="120">
         <v>5</v>
       </c>
-      <c r="C9" s="144" t="s">
+      <c r="C9" s="121" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="145"/>
-      <c r="E9" s="146">
+      <c r="D9" s="122"/>
+      <c r="E9" s="123">
         <v>104045.496</v>
       </c>
-      <c r="F9" s="147">
+      <c r="F9" s="124">
         <f>E9</f>
         <v>104045.496</v>
       </c>
-      <c r="G9" s="148">
+      <c r="G9" s="125">
         <f>E9-F9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="149">
+      <c r="H9" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="150">
-        <v>0</v>
-      </c>
-      <c r="J9" s="151">
+      <c r="I9" s="127">
+        <v>0</v>
+      </c>
+      <c r="J9" s="128">
         <f t="shared" si="1"/>
         <v>143638.91</v>
       </c>
-      <c r="K9" s="152">
+      <c r="K9" s="129">
         <f>K2*D9</f>
         <v>0</v>
       </c>
-      <c r="L9" s="150">
+      <c r="L9" s="127">
         <f>J9+K9+H9+G9</f>
         <v>143638.91</v>
       </c>
-      <c r="M9" s="153">
+      <c r="M9" s="130">
         <f t="shared" si="2"/>
         <v>149384.4664</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="154" t="s">
+    <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="155"/>
-      <c r="C10" s="156"/>
-      <c r="D10" s="157">
+      <c r="B10" s="132"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="134">
         <f t="shared" ref="D10:M10" si="4">SUM(D5:D9)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="159">
+      <c r="E10" s="136">
         <f t="shared" si="4"/>
         <v>810444.08319999999</v>
       </c>
-      <c r="F10" s="159">
+      <c r="F10" s="136">
         <f>SUM(F5:F9)</f>
         <v>702241.99200000009</v>
       </c>
-      <c r="G10" s="158">
+      <c r="G10" s="135">
         <f t="shared" si="4"/>
         <v>108202.09120000002</v>
       </c>
-      <c r="H10" s="159">
+      <c r="H10" s="136">
         <f t="shared" si="4"/>
         <v>4328.0836480000007</v>
       </c>
-      <c r="I10" s="162">
+      <c r="I10" s="139">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J10" s="161">
+      <c r="J10" s="138">
         <f t="shared" si="4"/>
         <v>718194.55</v>
       </c>
-      <c r="K10" s="160">
+      <c r="K10" s="137">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L10" s="159">
+      <c r="L10" s="136">
         <f t="shared" si="4"/>
         <v>830724.7248480001</v>
       </c>
-      <c r="M10" s="159">
+      <c r="M10" s="136">
         <f t="shared" si="4"/>
         <v>863953.71384192002</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="102"/>
-      <c r="B11" s="102"/>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102"/>
-      <c r="I11" s="102"/>
-      <c r="J11" s="102"/>
-      <c r="K11" s="102"/>
-      <c r="L11" s="102"/>
-      <c r="M11" s="102"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="144"/>
+      <c r="B11" s="144"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="144"/>
+      <c r="E11" s="144"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="144"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="144"/>
+      <c r="L11" s="144"/>
+      <c r="M11" s="144"/>
+    </row>
+    <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="103"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="103"/>
-      <c r="K13" s="103"/>
-      <c r="L13" s="103"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="103"/>
-      <c r="H14" s="103"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="103"/>
-      <c r="K14" s="103"/>
-      <c r="L14" s="103"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="103"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="103"/>
-      <c r="J15" s="103"/>
-      <c r="K15" s="103"/>
-      <c r="L15" s="103"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="103"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="103"/>
-      <c r="J16" s="103"/>
-      <c r="K16" s="103"/>
-      <c r="L16" s="103"/>
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="145"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="145"/>
+      <c r="I13" s="145"/>
+      <c r="J13" s="145"/>
+      <c r="K13" s="145"/>
+      <c r="L13" s="145"/>
+    </row>
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="145"/>
+      <c r="D14" s="145"/>
+      <c r="E14" s="145"/>
+      <c r="F14" s="145"/>
+      <c r="G14" s="145"/>
+      <c r="H14" s="145"/>
+      <c r="I14" s="145"/>
+      <c r="J14" s="145"/>
+      <c r="K14" s="145"/>
+      <c r="L14" s="145"/>
+    </row>
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="145"/>
+      <c r="D15" s="145"/>
+      <c r="E15" s="145"/>
+      <c r="F15" s="145"/>
+      <c r="G15" s="145"/>
+      <c r="H15" s="145"/>
+      <c r="I15" s="145"/>
+      <c r="J15" s="145"/>
+      <c r="K15" s="145"/>
+      <c r="L15" s="145"/>
+    </row>
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="145"/>
+      <c r="D16" s="145"/>
+      <c r="E16" s="145"/>
+      <c r="F16" s="145"/>
+      <c r="G16" s="145"/>
+      <c r="H16" s="145"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="145"/>
+      <c r="K16" s="145"/>
+      <c r="L16" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2931,60 +2935,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="151" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="111"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="153"/>
       <c r="F1" s="70"/>
       <c r="G1" s="70"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="154" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="115">
+      <c r="B2" s="155"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="157">
         <v>565</v>
       </c>
-      <c r="E2" s="116"/>
+      <c r="E2" s="158"/>
       <c r="F2" s="71"/>
       <c r="G2" s="71"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="117" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="117" t="s">
+      <c r="A3" s="159" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="159" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="117" t="s">
+      <c r="C3" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="119" t="s">
+      <c r="D3" s="161" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="104" t="s">
+      <c r="E3" s="146" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="104" t="s">
+      <c r="F3" s="146" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="104" t="s">
+      <c r="G3" s="146" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="118"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
+      <c r="A4" s="160"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="162"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="72">
@@ -3144,11 +3148,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="106"/>
-      <c r="B12" s="107"/>
-      <c r="C12" s="107"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="108"/>
+      <c r="A12" s="148"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="149"/>
+      <c r="D12" s="149"/>
+      <c r="E12" s="150"/>
       <c r="F12" s="70"/>
       <c r="G12" s="70"/>
     </row>
